--- a/test/Extract Pandat Results-P Ts (Lever Scheil)/Al-Cu-Li_COST/P.xlsx
+++ b/test/Extract Pandat Results-P Ts (Lever Scheil)/Al-Cu-Li_COST/P.xlsx
@@ -37,6 +37,15 @@
     <t>w(LI)</t>
   </si>
   <si>
+    <t>w(AL@LIQUID)</t>
+  </si>
+  <si>
+    <t>w(CU@LIQUID)</t>
+  </si>
+  <si>
+    <t>w(LI@LIQUID)</t>
+  </si>
+  <si>
     <t>w(AL@FCC_A1)</t>
   </si>
   <si>
@@ -44,15 +53,6 @@
   </si>
   <si>
     <t>w(LI@FCC_A1)</t>
-  </si>
-  <si>
-    <t>w(AL@LIQUID)</t>
-  </si>
-  <si>
-    <t>w(CU@LIQUID)</t>
-  </si>
-  <si>
-    <t>w(LI@LIQUID)</t>
   </si>
   <si>
     <t>w(AL@ALCULI_T2)</t>
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>93.61600806276149</v>
+        <v>93.6963819263792</v>
       </c>
       <c r="E2">
         <v>80</v>
@@ -585,22 +585,22 @@
         <v>4</v>
       </c>
       <c r="H2">
+        <v>80</v>
+      </c>
+      <c r="I2">
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
         <v>97.45415635000001</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>0.4222869798</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>2.123556673</v>
-      </c>
-      <c r="K2">
-        <v>80</v>
-      </c>
-      <c r="L2">
-        <v>16</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
       </c>
       <c r="AC2">
         <v>0.001862749698</v>
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>117.422940935541</v>
+        <v>117.527952997447</v>
       </c>
       <c r="E3">
         <v>79</v>
@@ -635,22 +635,22 @@
         <v>5</v>
       </c>
       <c r="H3">
+        <v>79</v>
+      </c>
+      <c r="I3">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
         <v>96.91084273</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>0.3181203562</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>2.771036911</v>
-      </c>
-      <c r="K3">
-        <v>79</v>
-      </c>
-      <c r="L3">
-        <v>16</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
       </c>
       <c r="AC3">
         <v>0.001523911934</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>48.0072670970452</v>
+        <v>48.0351257417592</v>
       </c>
       <c r="E4">
         <v>83</v>
@@ -685,19 +685,19 @@
         <v>0</v>
       </c>
       <c r="H4">
+        <v>83</v>
+      </c>
+      <c r="I4">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>98.0908374</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>1.909162595</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>83</v>
-      </c>
-      <c r="L4">
-        <v>17</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>51.0552989510299</v>
+        <v>51.0903498336371</v>
       </c>
       <c r="E5">
         <v>82</v>
@@ -732,22 +732,22 @@
         <v>1</v>
       </c>
       <c r="H5">
+        <v>82</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>98.2916931</v>
       </c>
-      <c r="I5">
+      <c r="L5">
         <v>1.210306284</v>
       </c>
-      <c r="J5">
+      <c r="M5">
         <v>0.4980006161</v>
-      </c>
-      <c r="K5">
-        <v>82</v>
-      </c>
-      <c r="L5">
-        <v>17</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
       <c r="AC5">
         <v>0.003188654571</v>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>61.8808187376732</v>
+        <v>61.9331682623429</v>
       </c>
       <c r="E6">
         <v>81</v>
@@ -782,22 +782,22 @@
         <v>2</v>
       </c>
       <c r="H6">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
         <v>98.16694318</v>
       </c>
-      <c r="I6">
+      <c r="L6">
         <v>0.8425009018</v>
       </c>
-      <c r="J6">
+      <c r="M6">
         <v>0.9905559197</v>
-      </c>
-      <c r="K6">
-        <v>81</v>
-      </c>
-      <c r="L6">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
       <c r="AC6">
         <v>0.002771648599</v>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>79.9368703373034</v>
+        <v>80.0080987064125</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -832,22 +832,22 @@
         <v>3</v>
       </c>
       <c r="H7">
+        <v>80</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>97.86067989999999</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>0.6167286238</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>1.52259148</v>
-      </c>
-      <c r="K7">
-        <v>80</v>
-      </c>
-      <c r="L7">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
       </c>
       <c r="AC7">
         <v>0.002232218921</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>102.864474321926</v>
+        <v>102.965414552932</v>
       </c>
       <c r="E8">
         <v>79</v>
@@ -882,22 +882,22 @@
         <v>4</v>
       </c>
       <c r="H8">
+        <v>79</v>
+      </c>
+      <c r="I8">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
         <v>97.42208451</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>0.461984779</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>2.115930714</v>
-      </c>
-      <c r="K8">
-        <v>79</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>4</v>
       </c>
       <c r="AC8">
         <v>0.00178906772</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>128.241097019805</v>
+        <v>128.371530831195</v>
       </c>
       <c r="E9">
         <v>78</v>
@@ -932,22 +932,22 @@
         <v>5</v>
       </c>
       <c r="H9">
+        <v>78</v>
+      </c>
+      <c r="I9">
+        <v>17</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
         <v>96.87412077</v>
       </c>
-      <c r="I9">
+      <c r="L9">
         <v>0.3474204992</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>2.778458727</v>
-      </c>
-      <c r="K9">
-        <v>78</v>
-      </c>
-      <c r="L9">
-        <v>17</v>
-      </c>
-      <c r="M9">
-        <v>5</v>
       </c>
       <c r="AC9">
         <v>0.001470224503</v>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>51.8042354459655</v>
+        <v>51.8375094086848</v>
       </c>
       <c r="E10">
         <v>82</v>
@@ -982,19 +982,19 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <v>82</v>
+      </c>
+      <c r="I10">
+        <v>18</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>97.94842137000001</v>
       </c>
-      <c r="I10">
+      <c r="L10">
         <v>2.051578626</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>82</v>
-      </c>
-      <c r="L10">
-        <v>18</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>55.6561444036823</v>
+        <v>55.6989094035286</v>
       </c>
       <c r="E11">
         <v>81</v>
@@ -1029,22 +1029,22 @@
         <v>1</v>
       </c>
       <c r="H11">
+        <v>81</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
         <v>98.20905042</v>
       </c>
-      <c r="I11">
+      <c r="L11">
         <v>1.308137132</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>0.482812445</v>
-      </c>
-      <c r="K11">
-        <v>81</v>
-      </c>
-      <c r="L11">
-        <v>18</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
       </c>
       <c r="AC11">
         <v>0.003089511527</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>14.95899938149</v>
+        <v>14.957369221867</v>
       </c>
       <c r="E12">
         <v>95</v>
@@ -1079,28 +1079,28 @@
         <v>4</v>
       </c>
       <c r="H12">
+        <v>95</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
         <v>97.55612173999999</v>
       </c>
-      <c r="I12">
+      <c r="L12">
         <v>0.01757244458</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>2.426305819</v>
-      </c>
-      <c r="K12">
-        <v>95</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>4</v>
       </c>
       <c r="AC12">
         <v>0.001708869707</v>
       </c>
       <c r="AD12">
-        <v>-0.0006569099863</v>
+        <v>-0.0006569099864</v>
       </c>
       <c r="AE12">
         <v>-0.00105195972</v>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>68.0517215951578</v>
+        <v>68.109749111174</v>
       </c>
       <c r="E13">
         <v>80</v>
@@ -1129,22 +1129,22 @@
         <v>2</v>
       </c>
       <c r="H13">
+        <v>80</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
         <v>98.11379047</v>
       </c>
-      <c r="I13">
+      <c r="L13">
         <v>0.9152152419</v>
       </c>
-      <c r="J13">
+      <c r="M13">
         <v>0.9709942902000001</v>
-      </c>
-      <c r="K13">
-        <v>80</v>
-      </c>
-      <c r="L13">
-        <v>18</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
       </c>
       <c r="AC13">
         <v>0.002659320599</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>87.996137134477</v>
+        <v>88.08530154150689</v>
       </c>
       <c r="E14">
         <v>79</v>
@@ -1179,22 +1179,22 @@
         <v>3</v>
       </c>
       <c r="H14">
+        <v>79</v>
+      </c>
+      <c r="I14">
+        <v>18</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
         <v>97.82136016</v>
       </c>
-      <c r="I14">
+      <c r="L14">
         <v>0.6720736336000001</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>1.506566209</v>
-      </c>
-      <c r="K14">
-        <v>79</v>
-      </c>
-      <c r="L14">
-        <v>18</v>
-      </c>
-      <c r="M14">
-        <v>3</v>
       </c>
       <c r="AC14">
         <v>0.002136591043</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>112.794984507471</v>
+        <v>112.920454782036</v>
       </c>
       <c r="E15">
         <v>78</v>
@@ -1229,22 +1229,22 @@
         <v>4</v>
       </c>
       <c r="H15">
+        <v>78</v>
+      </c>
+      <c r="I15">
+        <v>18</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
         <v>97.38615846</v>
       </c>
-      <c r="I15">
+      <c r="L15">
         <v>0.5037987195</v>
       </c>
-      <c r="J15">
+      <c r="M15">
         <v>2.110042823</v>
-      </c>
-      <c r="K15">
-        <v>78</v>
-      </c>
-      <c r="L15">
-        <v>18</v>
-      </c>
-      <c r="M15">
-        <v>4</v>
       </c>
       <c r="AC15">
         <v>0.001716719938</v>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>139.795285272356</v>
+        <v>139.95573593464</v>
       </c>
       <c r="E16">
         <v>77</v>
@@ -1279,22 +1279,22 @@
         <v>5</v>
       </c>
       <c r="H16">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="K16">
         <v>96.83364161</v>
       </c>
-      <c r="I16">
+      <c r="L16">
         <v>0.3780461164</v>
       </c>
-      <c r="J16">
+      <c r="M16">
         <v>2.788312273</v>
-      </c>
-      <c r="K16">
-        <v>77</v>
-      </c>
-      <c r="L16">
-        <v>18</v>
-      </c>
-      <c r="M16">
-        <v>5</v>
       </c>
       <c r="AC16">
         <v>0.001417092027</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>55.7829229560253</v>
+        <v>55.8222786933768</v>
       </c>
       <c r="E17">
         <v>81</v>
@@ -1329,19 +1329,19 @@
         <v>0</v>
       </c>
       <c r="H17">
+        <v>81</v>
+      </c>
+      <c r="I17">
+        <v>19</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>97.8000821</v>
       </c>
-      <c r="I17">
+      <c r="L17">
         <v>2.199917902</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>81</v>
-      </c>
-      <c r="L17">
-        <v>19</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>60.5832534757298</v>
+        <v>60.6349970852381</v>
       </c>
       <c r="E18">
         <v>80</v>
@@ -1376,22 +1376,22 @@
         <v>1</v>
       </c>
       <c r="H18">
+        <v>80</v>
+      </c>
+      <c r="I18">
+        <v>19</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
         <v>98.12096517000001</v>
       </c>
-      <c r="I18">
+      <c r="L18">
         <v>1.410725401</v>
       </c>
-      <c r="J18">
+      <c r="M18">
         <v>0.4683094279</v>
-      </c>
-      <c r="K18">
-        <v>80</v>
-      </c>
-      <c r="L18">
-        <v>19</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
       </c>
       <c r="AC18">
         <v>0.002988371663</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>74.700838267752</v>
+        <v>74.7728107955238</v>
       </c>
       <c r="E19">
         <v>79</v>
@@ -1426,22 +1426,22 @@
         <v>2</v>
       </c>
       <c r="H19">
+        <v>79</v>
+      </c>
+      <c r="I19">
+        <v>19</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
         <v>98.05570716</v>
       </c>
-      <c r="I19">
+      <c r="L19">
         <v>0.9918647816</v>
       </c>
-      <c r="J19">
+      <c r="M19">
         <v>0.9524280585</v>
-      </c>
-      <c r="K19">
-        <v>79</v>
-      </c>
-      <c r="L19">
-        <v>19</v>
-      </c>
-      <c r="M19">
-        <v>2</v>
       </c>
       <c r="AC19">
         <v>0.002548312114</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>96.67579016997431</v>
+        <v>96.78636363456771</v>
       </c>
       <c r="E20">
         <v>78</v>
@@ -1476,22 +1476,22 @@
         <v>3</v>
       </c>
       <c r="H20">
+        <v>78</v>
+      </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
         <v>97.77763503</v>
       </c>
-      <c r="I20">
+      <c r="L20">
         <v>0.7305279055</v>
       </c>
-      <c r="J20">
+      <c r="M20">
         <v>1.491837061</v>
-      </c>
-      <c r="K20">
-        <v>78</v>
-      </c>
-      <c r="L20">
-        <v>19</v>
-      </c>
-      <c r="M20">
-        <v>3</v>
       </c>
       <c r="AC20">
         <v>0.002043313687</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>123.442381140788</v>
+        <v>123.596954170491</v>
       </c>
       <c r="E21">
         <v>77</v>
@@ -1526,22 +1526,22 @@
         <v>4</v>
       </c>
       <c r="H21">
+        <v>77</v>
+      </c>
+      <c r="I21">
+        <v>19</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
         <v>97.34620663</v>
       </c>
-      <c r="I21">
+      <c r="L21">
         <v>0.5478437852</v>
       </c>
-      <c r="J21">
+      <c r="M21">
         <v>2.105949585</v>
-      </c>
-      <c r="K21">
-        <v>77</v>
-      </c>
-      <c r="L21">
-        <v>19</v>
-      </c>
-      <c r="M21">
-        <v>4</v>
       </c>
       <c r="AC21">
         <v>0.001646102747</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>152.115992283898</v>
+        <v>152.310818796128</v>
       </c>
       <c r="E22">
         <v>76</v>
@@ -1576,22 +1576,22 @@
         <v>5</v>
       </c>
       <c r="H22">
+        <v>76</v>
+      </c>
+      <c r="I22">
+        <v>19</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
+      <c r="K22">
         <v>96.78925568</v>
       </c>
-      <c r="I22">
+      <c r="L22">
         <v>0.4100153802</v>
       </c>
-      <c r="J22">
+      <c r="M22">
         <v>2.800728944</v>
-      </c>
-      <c r="K22">
-        <v>76</v>
-      </c>
-      <c r="L22">
-        <v>19</v>
-      </c>
-      <c r="M22">
-        <v>5</v>
       </c>
       <c r="AC22">
         <v>0.00136487437</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>23.3177681548973</v>
+        <v>23.3170845378262</v>
       </c>
       <c r="E23">
         <v>94</v>
@@ -1626,22 +1626,22 @@
         <v>5</v>
       </c>
       <c r="H23">
+        <v>94</v>
+      </c>
+      <c r="I23">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23">
         <v>97.09070939999999</v>
       </c>
-      <c r="I23">
+      <c r="L23">
         <v>0.01316915537</v>
       </c>
-      <c r="J23">
+      <c r="M23">
         <v>2.896121443</v>
-      </c>
-      <c r="K23">
-        <v>94</v>
-      </c>
-      <c r="L23">
-        <v>0.9999999999</v>
-      </c>
-      <c r="M23">
-        <v>5</v>
       </c>
       <c r="AC23">
         <v>0.001325457152</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>59.9579757140785</v>
+        <v>60.0041538226146</v>
       </c>
       <c r="E24">
         <v>80</v>
@@ -1676,19 +1676,19 @@
         <v>0</v>
       </c>
       <c r="H24">
+        <v>80</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>97.64512769</v>
       </c>
-      <c r="I24">
+      <c r="L24">
         <v>2.354872305</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>80</v>
-      </c>
-      <c r="L24">
-        <v>20</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>65.8634990105141</v>
+        <v>65.9256799793081</v>
       </c>
       <c r="E25">
         <v>79</v>
@@ -1723,31 +1723,31 @@
         <v>1</v>
       </c>
       <c r="H25">
+        <v>79</v>
+      </c>
+      <c r="I25">
+        <v>20</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
         <v>98.02700110000001</v>
       </c>
-      <c r="I25">
+      <c r="L25">
         <v>1.518533697</v>
       </c>
-      <c r="J25">
+      <c r="M25">
         <v>0.4544652046</v>
       </c>
-      <c r="K25">
-        <v>79</v>
-      </c>
-      <c r="L25">
-        <v>20</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
       <c r="AC25">
-        <v>0.002885975291</v>
+        <v>0.002885975292</v>
       </c>
       <c r="AD25">
-        <v>-0.002803228639</v>
+        <v>-0.00280322864</v>
       </c>
       <c r="AE25">
-        <v>-8.27466519E-05</v>
+        <v>-8.274665192E-05</v>
       </c>
     </row>
     <row r="26" spans="1:31">
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>81.8677302987011</v>
+        <v>81.9562437428273</v>
       </c>
       <c r="E26">
         <v>78</v>
@@ -1773,28 +1773,28 @@
         <v>2</v>
       </c>
       <c r="H26">
+        <v>78</v>
+      </c>
+      <c r="I26">
+        <v>20</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
         <v>97.9923764</v>
       </c>
-      <c r="I26">
+      <c r="L26">
         <v>1.072787751</v>
       </c>
-      <c r="J26">
+      <c r="M26">
         <v>0.9348358453</v>
-      </c>
-      <c r="K26">
-        <v>78</v>
-      </c>
-      <c r="L26">
-        <v>20</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
       </c>
       <c r="AC26">
         <v>0.002439239241</v>
       </c>
       <c r="AD26">
-        <v>-0.00230928229</v>
+        <v>-0.002309282289</v>
       </c>
       <c r="AE26">
         <v>-0.0001299569512</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>106.012038566939</v>
+        <v>106.148046384627</v>
       </c>
       <c r="E27">
         <v>77</v>
@@ -1823,22 +1823,22 @@
         <v>3</v>
       </c>
       <c r="H27">
+        <v>77</v>
+      </c>
+      <c r="I27">
+        <v>20</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
         <v>97.72926474</v>
       </c>
-      <c r="I27">
+      <c r="L27">
         <v>0.7923228328</v>
       </c>
-      <c r="J27">
+      <c r="M27">
         <v>1.478412432</v>
-      </c>
-      <c r="K27">
-        <v>77</v>
-      </c>
-      <c r="L27">
-        <v>20</v>
-      </c>
-      <c r="M27">
-        <v>3</v>
       </c>
       <c r="AC27">
         <v>0.001952755488</v>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>134.841993490926</v>
+        <v>135.030923669618</v>
       </c>
       <c r="E28">
         <v>76</v>
@@ -1873,28 +1873,28 @@
         <v>4</v>
       </c>
       <c r="H28">
+        <v>76</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28">
         <v>97.30204406</v>
       </c>
-      <c r="I28">
+      <c r="L28">
         <v>0.5942397185</v>
       </c>
-      <c r="J28">
+      <c r="M28">
         <v>2.103716219</v>
       </c>
-      <c r="K28">
-        <v>76</v>
-      </c>
-      <c r="L28">
-        <v>20</v>
-      </c>
-      <c r="M28">
-        <v>4</v>
-      </c>
       <c r="AC28">
-        <v>0.001577503133</v>
+        <v>0.001577503132</v>
       </c>
       <c r="AD28">
-        <v>-0.001437081511</v>
+        <v>-0.00143708151</v>
       </c>
       <c r="AE28">
         <v>-0.0001404216219</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>165.233427761932</v>
+        <v>165.470556202342</v>
       </c>
       <c r="E29">
         <v>75</v>
@@ -1923,25 +1923,25 @@
         <v>5</v>
       </c>
       <c r="H29">
+        <v>75</v>
+      </c>
+      <c r="I29">
+        <v>20</v>
+      </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
+      <c r="K29">
         <v>96.7408071</v>
       </c>
-      <c r="I29">
+      <c r="L29">
         <v>0.4433364279</v>
       </c>
-      <c r="J29">
+      <c r="M29">
         <v>2.815856475</v>
       </c>
-      <c r="K29">
-        <v>75</v>
-      </c>
-      <c r="L29">
-        <v>20</v>
-      </c>
-      <c r="M29">
-        <v>5</v>
-      </c>
       <c r="AC29">
-        <v>0.001313842569</v>
+        <v>0.001313842568</v>
       </c>
       <c r="AD29">
         <v>-0.001181856535</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>4.74402869014326</v>
+        <v>4.73950514272145</v>
       </c>
       <c r="E30">
         <v>98</v>
@@ -1973,19 +1973,19 @@
         <v>0</v>
       </c>
       <c r="H30">
+        <v>98</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>99.80494656</v>
       </c>
-      <c r="I30">
+      <c r="L30">
         <v>0.1950534381</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>98</v>
-      </c>
-      <c r="L30">
-        <v>2</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>5.15157648217004</v>
+        <v>5.14721996503869</v>
       </c>
       <c r="E31">
         <v>97</v>
@@ -2020,22 +2020,22 @@
         <v>1</v>
       </c>
       <c r="H31">
+        <v>97</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
         <v>99.0592977</v>
       </c>
-      <c r="I31">
+      <c r="L31">
         <v>0.1128308441</v>
       </c>
-      <c r="J31">
+      <c r="M31">
         <v>0.8278714523</v>
-      </c>
-      <c r="K31">
-        <v>97</v>
-      </c>
-      <c r="L31">
-        <v>2</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
       </c>
       <c r="AC31">
         <v>0.004000667595</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>7.05822525346353</v>
+        <v>7.05499496153202</v>
       </c>
       <c r="E32">
         <v>96</v>
@@ -2070,22 +2070,22 @@
         <v>2</v>
       </c>
       <c r="H32">
+        <v>96</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
         <v>98.506506</v>
       </c>
-      <c r="I32">
+      <c r="L32">
         <v>0.07216648031</v>
       </c>
-      <c r="J32">
+      <c r="M32">
         <v>1.421327522</v>
-      </c>
-      <c r="K32">
-        <v>96</v>
-      </c>
-      <c r="L32">
-        <v>2</v>
-      </c>
-      <c r="M32">
-        <v>2</v>
       </c>
       <c r="AC32">
         <v>0.003552865436</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>11.1877875769818</v>
+        <v>11.1855086761047</v>
       </c>
       <c r="E33">
         <v>95</v>
@@ -2120,22 +2120,22 @@
         <v>3</v>
       </c>
       <c r="H33">
+        <v>95</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33">
         <v>98.02877952</v>
       </c>
-      <c r="I33">
+      <c r="L33">
         <v>0.04970722423</v>
       </c>
-      <c r="J33">
+      <c r="M33">
         <v>1.921513258</v>
-      </c>
-      <c r="K33">
-        <v>95</v>
-      </c>
-      <c r="L33">
-        <v>2</v>
-      </c>
-      <c r="M33">
-        <v>3</v>
       </c>
       <c r="AC33">
         <v>0.002707753063</v>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>17.7282517334595</v>
+        <v>17.726867925503</v>
       </c>
       <c r="E34">
         <v>94</v>
@@ -2170,22 +2170,22 @@
         <v>4</v>
       </c>
       <c r="H34">
+        <v>94</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>4</v>
+      </c>
+      <c r="K34">
         <v>97.56837173</v>
       </c>
-      <c r="I34">
+      <c r="L34">
         <v>0.03604806278</v>
       </c>
-      <c r="J34">
+      <c r="M34">
         <v>2.39558021</v>
-      </c>
-      <c r="K34">
-        <v>94</v>
-      </c>
-      <c r="L34">
-        <v>2</v>
-      </c>
-      <c r="M34">
-        <v>4</v>
       </c>
       <c r="AC34">
         <v>0.002012918866</v>
@@ -2194,7 +2194,7 @@
         <v>-0.00110798546</v>
       </c>
       <c r="AE34">
-        <v>-0.000904933406</v>
+        <v>-0.0009049334059</v>
       </c>
     </row>
     <row r="35" spans="1:31">
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>26.594520089407</v>
+        <v>26.5944841883531</v>
       </c>
       <c r="E35">
         <v>93</v>
@@ -2220,31 +2220,31 @@
         <v>5</v>
       </c>
       <c r="H35">
+        <v>93</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>5</v>
+      </c>
+      <c r="K35">
         <v>97.09719735</v>
       </c>
-      <c r="I35">
+      <c r="L35">
         <v>0.02705600425</v>
       </c>
-      <c r="J35">
+      <c r="M35">
         <v>2.875746647</v>
-      </c>
-      <c r="K35">
-        <v>93</v>
-      </c>
-      <c r="L35">
-        <v>2</v>
-      </c>
-      <c r="M35">
-        <v>5</v>
       </c>
       <c r="AC35">
         <v>0.001540574441</v>
       </c>
       <c r="AD35">
-        <v>-0.0007419077836</v>
+        <v>-0.0007419077837</v>
       </c>
       <c r="AE35">
-        <v>-0.0007986666575</v>
+        <v>-0.0007986666576</v>
       </c>
     </row>
     <row r="36" spans="1:31">
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>7.15797250027194</v>
+        <v>7.15371975146066</v>
       </c>
       <c r="E36">
         <v>97</v>
@@ -2270,19 +2270,19 @@
         <v>0</v>
       </c>
       <c r="H36">
+        <v>97</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
         <v>99.70566209</v>
       </c>
-      <c r="I36">
+      <c r="L36">
         <v>0.2943379112</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>97</v>
-      </c>
-      <c r="L36">
-        <v>3</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>7.58536367735564</v>
+        <v>7.58123613791508</v>
       </c>
       <c r="E37">
         <v>96</v>
@@ -2317,22 +2317,22 @@
         <v>1</v>
       </c>
       <c r="H37">
+        <v>96</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
         <v>99.02983539</v>
       </c>
-      <c r="I37">
+      <c r="L37">
         <v>0.1713259976</v>
       </c>
-      <c r="J37">
+      <c r="M37">
         <v>0.7988386169</v>
-      </c>
-      <c r="K37">
-        <v>96</v>
-      </c>
-      <c r="L37">
-        <v>3</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
       </c>
       <c r="AC37">
         <v>0.003996433768</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0.253637222709254</v>
+        <v>0.253577491707227</v>
       </c>
       <c r="E38">
         <v>99</v>
@@ -2367,22 +2367,22 @@
         <v>1</v>
       </c>
       <c r="H38">
+        <v>99</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
         <v>99.1105024</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>0.8894975993000001</v>
-      </c>
-      <c r="K38">
-        <v>99</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
       </c>
       <c r="AC38">
         <v>0.004336611661</v>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>9.470985275259229</v>
+        <v>9.46781756624627</v>
       </c>
       <c r="E39">
         <v>95</v>
@@ -2414,22 +2414,22 @@
         <v>2</v>
       </c>
       <c r="H39">
+        <v>95</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39">
         <v>98.50620154000001</v>
       </c>
-      <c r="I39">
+      <c r="L39">
         <v>0.1102300427</v>
       </c>
-      <c r="J39">
+      <c r="M39">
         <v>1.383568421</v>
-      </c>
-      <c r="K39">
-        <v>95</v>
-      </c>
-      <c r="L39">
-        <v>3</v>
-      </c>
-      <c r="M39">
-        <v>2</v>
       </c>
       <c r="AC39">
         <v>0.003703265552</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>13.7747143353286</v>
+        <v>13.7726637403822</v>
       </c>
       <c r="E40">
         <v>94</v>
@@ -2464,22 +2464,22 @@
         <v>3</v>
       </c>
       <c r="H40">
+        <v>94</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
         <v>98.03850336000001</v>
       </c>
-      <c r="I40">
+      <c r="L40">
         <v>0.07626871440000001</v>
       </c>
-      <c r="J40">
+      <c r="M40">
         <v>1.885227923</v>
-      </c>
-      <c r="K40">
-        <v>94</v>
-      </c>
-      <c r="L40">
-        <v>3</v>
-      </c>
-      <c r="M40">
-        <v>3</v>
       </c>
       <c r="AC40">
         <v>0.002932197182</v>
@@ -2488,7 +2488,7 @@
         <v>-0.002122964536</v>
       </c>
       <c r="AE40">
-        <v>-0.0008092326465</v>
+        <v>-0.0008092326464</v>
       </c>
     </row>
     <row r="41" spans="1:31">
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>20.7327393839992</v>
+        <v>20.7319406035633</v>
       </c>
       <c r="E41">
         <v>93</v>
@@ -2514,22 +2514,22 @@
         <v>4</v>
       </c>
       <c r="H41">
+        <v>93</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41">
         <v>97.57817314</v>
       </c>
-      <c r="I41">
+      <c r="L41">
         <v>0.05547446248</v>
       </c>
-      <c r="J41">
+      <c r="M41">
         <v>2.366352393</v>
-      </c>
-      <c r="K41">
-        <v>93</v>
-      </c>
-      <c r="L41">
-        <v>3</v>
-      </c>
-      <c r="M41">
-        <v>4</v>
       </c>
       <c r="AC41">
         <v>0.002208202079</v>
@@ -2538,7 +2538,7 @@
         <v>-0.001420343452</v>
       </c>
       <c r="AE41">
-        <v>-0.0007878586268</v>
+        <v>-0.0007878586269</v>
       </c>
     </row>
     <row r="42" spans="1:31">
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>30.1854591591361</v>
+        <v>30.1864475565858</v>
       </c>
       <c r="E42">
         <v>92</v>
@@ -2564,22 +2564,22 @@
         <v>5</v>
       </c>
       <c r="H42">
+        <v>92</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+      <c r="K42">
         <v>97.10134404999999</v>
       </c>
-      <c r="I42">
+      <c r="L42">
         <v>0.04169497664</v>
       </c>
-      <c r="J42">
+      <c r="M42">
         <v>2.856960976</v>
-      </c>
-      <c r="K42">
-        <v>92</v>
-      </c>
-      <c r="L42">
-        <v>3</v>
-      </c>
-      <c r="M42">
-        <v>5</v>
       </c>
       <c r="AC42">
         <v>0.00168989847</v>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>9.60780504546204</v>
+        <v>9.60401355394484</v>
       </c>
       <c r="E43">
         <v>96</v>
@@ -2614,19 +2614,19 @@
         <v>0</v>
       </c>
       <c r="H43">
+        <v>96</v>
+      </c>
+      <c r="I43">
+        <v>4</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
         <v>99.60504840999999</v>
       </c>
-      <c r="I43">
+      <c r="L43">
         <v>0.3949515947</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>96</v>
-      </c>
-      <c r="L43">
-        <v>4</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>10.0304136890513</v>
+        <v>10.026751996064</v>
       </c>
       <c r="E44">
         <v>95</v>
@@ -2661,22 +2661,22 @@
         <v>1</v>
       </c>
       <c r="H44">
+        <v>95</v>
+      </c>
+      <c r="I44">
+        <v>4</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
         <v>98.99772652</v>
       </c>
-      <c r="I44">
+      <c r="L44">
         <v>0.231322897</v>
       </c>
-      <c r="J44">
+      <c r="M44">
         <v>0.7709505839</v>
-      </c>
-      <c r="K44">
-        <v>95</v>
-      </c>
-      <c r="L44">
-        <v>4</v>
-      </c>
-      <c r="M44">
-        <v>1</v>
       </c>
       <c r="AC44">
         <v>0.003987016154</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>11.9528857586642</v>
+        <v>11.9501168900699</v>
       </c>
       <c r="E45">
         <v>94</v>
@@ -2711,22 +2711,22 @@
         <v>2</v>
       </c>
       <c r="H45">
+        <v>94</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
         <v>98.50305317999999</v>
       </c>
-      <c r="I45">
+      <c r="L45">
         <v>0.1497124953</v>
       </c>
-      <c r="J45">
+      <c r="M45">
         <v>1.347234328</v>
-      </c>
-      <c r="K45">
-        <v>94</v>
-      </c>
-      <c r="L45">
-        <v>4</v>
-      </c>
-      <c r="M45">
-        <v>2</v>
       </c>
       <c r="AC45">
         <v>0.003768136489</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>16.5272098325647</v>
+        <v>16.5257411158794</v>
       </c>
       <c r="E46">
         <v>93</v>
@@ -2761,22 +2761,22 @@
         <v>3</v>
       </c>
       <c r="H46">
+        <v>93</v>
+      </c>
+      <c r="I46">
+        <v>4</v>
+      </c>
+      <c r="J46">
+        <v>3</v>
+      </c>
+      <c r="K46">
         <v>98.04554387</v>
       </c>
-      <c r="I46">
+      <c r="L46">
         <v>0.1040526984</v>
       </c>
-      <c r="J46">
+      <c r="M46">
         <v>1.850403433</v>
-      </c>
-      <c r="K46">
-        <v>93</v>
-      </c>
-      <c r="L46">
-        <v>4</v>
-      </c>
-      <c r="M46">
-        <v>3</v>
       </c>
       <c r="AC46">
         <v>0.003053033287</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>23.998035969038</v>
+        <v>23.9982100954164</v>
       </c>
       <c r="E47">
         <v>92</v>
@@ -2811,22 +2811,22 @@
         <v>4</v>
       </c>
       <c r="H47">
+        <v>92</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47">
         <v>97.58548041</v>
       </c>
-      <c r="I47">
+      <c r="L47">
         <v>0.0759021616</v>
       </c>
-      <c r="J47">
+      <c r="M47">
         <v>2.338617427</v>
-      </c>
-      <c r="K47">
-        <v>92</v>
-      </c>
-      <c r="L47">
-        <v>4</v>
-      </c>
-      <c r="M47">
-        <v>4</v>
       </c>
       <c r="AC47">
         <v>0.002327368955</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>34.1152976624126</v>
+        <v>34.1177686345519</v>
       </c>
       <c r="E48">
         <v>91</v>
@@ -2861,22 +2861,22 @@
         <v>5</v>
       </c>
       <c r="H48">
+        <v>91</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="J48">
+        <v>5</v>
+      </c>
+      <c r="K48">
         <v>97.10309672</v>
       </c>
-      <c r="I48">
+      <c r="L48">
         <v>0.05712184422</v>
       </c>
-      <c r="J48">
+      <c r="M48">
         <v>2.83978144</v>
-      </c>
-      <c r="K48">
-        <v>91</v>
-      </c>
-      <c r="L48">
-        <v>4</v>
-      </c>
-      <c r="M48">
-        <v>5</v>
       </c>
       <c r="AC48">
         <v>0.001788779541</v>
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>2.34883356467889</v>
+        <v>2.3476236866624</v>
       </c>
       <c r="E49">
         <v>98</v>
@@ -2911,22 +2911,22 @@
         <v>2</v>
       </c>
       <c r="H49">
+        <v>98</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49">
         <v>98.49875898000001</v>
       </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>1.501241019</v>
-      </c>
-      <c r="K49">
-        <v>98</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>2</v>
       </c>
       <c r="AC49">
         <v>0.002123547691</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>12.0990357798499</v>
+        <v>12.0959165343704</v>
       </c>
       <c r="E50">
         <v>95</v>
@@ -2958,19 +2958,19 @@
         <v>0</v>
       </c>
       <c r="H50">
+        <v>95</v>
+      </c>
+      <c r="I50">
+        <v>5</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
         <v>99.50297218999999</v>
       </c>
-      <c r="I50">
+      <c r="L50">
         <v>0.4970278097</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>95</v>
-      </c>
-      <c r="L50">
-        <v>5</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>12.5026281311098</v>
+        <v>12.4996678669411</v>
       </c>
       <c r="E51">
         <v>94</v>
@@ -3005,22 +3005,22 @@
         <v>1</v>
       </c>
       <c r="H51">
+        <v>94</v>
+      </c>
+      <c r="I51">
+        <v>5</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
         <v>98.96290505</v>
       </c>
-      <c r="I51">
+      <c r="L51">
         <v>0.2929196791</v>
       </c>
-      <c r="J51">
+      <c r="M51">
         <v>0.7441752686000001</v>
-      </c>
-      <c r="K51">
-        <v>94</v>
-      </c>
-      <c r="L51">
-        <v>5</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
       </c>
       <c r="AC51">
         <v>0.003970382745</v>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>14.5271765579662</v>
+        <v>14.5251185016727</v>
       </c>
       <c r="E52">
         <v>93</v>
@@ -3055,22 +3055,22 @@
         <v>2</v>
       </c>
       <c r="H52">
+        <v>93</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
         <v>98.49700924</v>
       </c>
-      <c r="I52">
+      <c r="L52">
         <v>0.1906963392</v>
       </c>
-      <c r="J52">
+      <c r="M52">
         <v>1.312294417</v>
-      </c>
-      <c r="K52">
-        <v>93</v>
-      </c>
-      <c r="L52">
-        <v>5</v>
-      </c>
-      <c r="M52">
-        <v>2</v>
       </c>
       <c r="AC52">
         <v>0.003784377849</v>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>19.4711375375763</v>
+        <v>19.4706272074745</v>
       </c>
       <c r="E53">
         <v>92</v>
@@ -3105,22 +3105,22 @@
         <v>3</v>
       </c>
       <c r="H53">
+        <v>92</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>3</v>
+      </c>
+      <c r="K53">
         <v>98.04985252</v>
       </c>
-      <c r="I53">
+      <c r="L53">
         <v>0.1331281314</v>
       </c>
-      <c r="J53">
+      <c r="M53">
         <v>1.817019351</v>
-      </c>
-      <c r="K53">
-        <v>92</v>
-      </c>
-      <c r="L53">
-        <v>5</v>
-      </c>
-      <c r="M53">
-        <v>3</v>
       </c>
       <c r="AC53">
         <v>0.003107021056</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>27.5502339793951</v>
+        <v>27.5518365853984</v>
       </c>
       <c r="E54">
         <v>91</v>
@@ -3155,22 +3155,22 @@
         <v>4</v>
       </c>
       <c r="H54">
+        <v>91</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
+      <c r="K54">
         <v>97.59024316999999</v>
       </c>
-      <c r="I54">
+      <c r="L54">
         <v>0.09738475874999999</v>
       </c>
-      <c r="J54">
+      <c r="M54">
         <v>2.312372069</v>
-      </c>
-      <c r="K54">
-        <v>91</v>
-      </c>
-      <c r="L54">
-        <v>5</v>
-      </c>
-      <c r="M54">
-        <v>4</v>
       </c>
       <c r="AC54">
         <v>0.002391840238</v>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>38.409251427558</v>
+        <v>38.4137645892995</v>
       </c>
       <c r="E55">
         <v>90</v>
@@ -3205,22 +3205,22 @@
         <v>5</v>
       </c>
       <c r="H55">
+        <v>90</v>
+      </c>
+      <c r="I55">
+        <v>5</v>
+      </c>
+      <c r="J55">
+        <v>5</v>
+      </c>
+      <c r="K55">
         <v>97.10239785</v>
       </c>
-      <c r="I55">
+      <c r="L55">
         <v>0.07337368545</v>
       </c>
-      <c r="J55">
+      <c r="M55">
         <v>2.824228467</v>
-      </c>
-      <c r="K55">
-        <v>90</v>
-      </c>
-      <c r="L55">
-        <v>5</v>
-      </c>
-      <c r="M55">
-        <v>5</v>
       </c>
       <c r="AC55">
         <v>0.001848871303</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>14.6377250383634</v>
+        <v>14.6355018026317</v>
       </c>
       <c r="E56">
         <v>94</v>
@@ -3255,19 +3255,19 @@
         <v>0</v>
       </c>
       <c r="H56">
+        <v>94</v>
+      </c>
+      <c r="I56">
+        <v>6</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
         <v>99.39928637</v>
       </c>
-      <c r="I56">
+      <c r="L56">
         <v>0.6007136312</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>94</v>
-      </c>
-      <c r="L56">
-        <v>6</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>15.0186130348282</v>
+        <v>15.0165981545961</v>
       </c>
       <c r="E57">
         <v>93</v>
@@ -3302,22 +3302,22 @@
         <v>1</v>
       </c>
       <c r="H57">
+        <v>93</v>
+      </c>
+      <c r="I57">
+        <v>6</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
         <v>98.92529485999999</v>
       </c>
-      <c r="I57">
+      <c r="L57">
         <v>0.3562248092</v>
       </c>
-      <c r="J57">
+      <c r="M57">
         <v>0.7184803258</v>
-      </c>
-      <c r="K57">
-        <v>93</v>
-      </c>
-      <c r="L57">
-        <v>6</v>
-      </c>
-      <c r="M57">
-        <v>1</v>
       </c>
       <c r="AC57">
         <v>0.003945760278</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>17.2176069207258</v>
+        <v>17.21658277955</v>
       </c>
       <c r="E58">
         <v>92</v>
@@ -3352,22 +3352,22 @@
         <v>2</v>
       </c>
       <c r="H58">
+        <v>92</v>
+      </c>
+      <c r="I58">
+        <v>6</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="K58">
         <v>98.48801090000001</v>
       </c>
-      <c r="I58">
+      <c r="L58">
         <v>0.2332715982</v>
       </c>
-      <c r="J58">
+      <c r="M58">
         <v>1.2787175</v>
-      </c>
-      <c r="K58">
-        <v>92</v>
-      </c>
-      <c r="L58">
-        <v>6</v>
-      </c>
-      <c r="M58">
-        <v>2</v>
       </c>
       <c r="AC58">
         <v>0.003768322469</v>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>22.6328651871389</v>
+        <v>22.6337364893029</v>
       </c>
       <c r="E59">
         <v>91</v>
@@ -3402,22 +3402,22 @@
         <v>3</v>
       </c>
       <c r="H59">
+        <v>91</v>
+      </c>
+      <c r="I59">
+        <v>6</v>
+      </c>
+      <c r="J59">
+        <v>3</v>
+      </c>
+      <c r="K59">
         <v>98.05137498000001</v>
       </c>
-      <c r="I59">
+      <c r="L59">
         <v>0.1635692672</v>
       </c>
-      <c r="J59">
+      <c r="M59">
         <v>1.785055754</v>
-      </c>
-      <c r="K59">
-        <v>91</v>
-      </c>
-      <c r="L59">
-        <v>6</v>
-      </c>
-      <c r="M59">
-        <v>3</v>
       </c>
       <c r="AC59">
         <v>0.003115273409</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>6.40942499367027</v>
+        <v>6.40789901339593</v>
       </c>
       <c r="E60">
         <v>97</v>
@@ -3452,22 +3452,22 @@
         <v>3</v>
       </c>
       <c r="H60">
+        <v>97</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3</v>
+      </c>
+      <c r="K60">
         <v>98.00145034000001</v>
       </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>1.998549661</v>
-      </c>
-      <c r="K60">
-        <v>97</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>3</v>
       </c>
       <c r="AC60">
         <v>0.001562515225</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>31.4159605215354</v>
+        <v>31.4195350265651</v>
       </c>
       <c r="E61">
         <v>90</v>
@@ -3499,22 +3499,22 @@
         <v>4</v>
       </c>
       <c r="H61">
+        <v>90</v>
+      </c>
+      <c r="I61">
+        <v>6</v>
+      </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
+      <c r="K61">
         <v>97.59240586999999</v>
       </c>
-      <c r="I61">
+      <c r="L61">
         <v>0.1199791107</v>
       </c>
-      <c r="J61">
+      <c r="M61">
         <v>2.287615017</v>
-      </c>
-      <c r="K61">
-        <v>90</v>
-      </c>
-      <c r="L61">
-        <v>6</v>
-      </c>
-      <c r="M61">
-        <v>4</v>
       </c>
       <c r="AC61">
         <v>0.002416340258</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>43.0930644297734</v>
+        <v>43.1003016900493</v>
       </c>
       <c r="E62">
         <v>89</v>
@@ -3549,22 +3549,22 @@
         <v>5</v>
       </c>
       <c r="H62">
+        <v>89</v>
+      </c>
+      <c r="I62">
+        <v>6</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62">
         <v>97.09918492</v>
       </c>
-      <c r="I62">
+      <c r="L62">
         <v>0.09048882693</v>
       </c>
-      <c r="J62">
+      <c r="M62">
         <v>2.810326253</v>
-      </c>
-      <c r="K62">
-        <v>89</v>
-      </c>
-      <c r="L62">
-        <v>6</v>
-      </c>
-      <c r="M62">
-        <v>5</v>
       </c>
       <c r="AC62">
         <v>0.001879081287</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>17.2303562605973</v>
+        <v>17.2292651542019</v>
       </c>
       <c r="E63">
         <v>93</v>
@@ -3599,19 +3599,19 @@
         <v>0</v>
       </c>
       <c r="H63">
+        <v>93</v>
+      </c>
+      <c r="I63">
+        <v>7</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
         <v>99.29382862999999</v>
       </c>
-      <c r="I63">
+      <c r="L63">
         <v>0.7061713736</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>93</v>
-      </c>
-      <c r="L63">
-        <v>7</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>17.5956870265665</v>
+        <v>17.594877565626</v>
       </c>
       <c r="E64">
         <v>92</v>
@@ -3646,22 +3646,22 @@
         <v>1</v>
       </c>
       <c r="H64">
+        <v>92</v>
+      </c>
+      <c r="I64">
+        <v>7</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
         <v>98.88480868000001</v>
       </c>
-      <c r="I64">
+      <c r="L64">
         <v>0.4213580138</v>
       </c>
-      <c r="J64">
+      <c r="M64">
         <v>0.6938333017</v>
-      </c>
-      <c r="K64">
-        <v>92</v>
-      </c>
-      <c r="L64">
-        <v>7</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
       </c>
       <c r="AC64">
         <v>0.00391288743</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>20.0485734952579</v>
+        <v>20.0489379379565</v>
       </c>
       <c r="E65">
         <v>91</v>
@@ -3696,22 +3696,22 @@
         <v>2</v>
       </c>
       <c r="H65">
+        <v>91</v>
+      </c>
+      <c r="I65">
+        <v>7</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65">
         <v>98.47599129</v>
       </c>
-      <c r="I65">
+      <c r="L65">
         <v>0.2775365033</v>
       </c>
-      <c r="J65">
+      <c r="M65">
         <v>1.246472209</v>
-      </c>
-      <c r="K65">
-        <v>91</v>
-      </c>
-      <c r="L65">
-        <v>7</v>
-      </c>
-      <c r="M65">
-        <v>2</v>
       </c>
       <c r="AC65">
         <v>0.003728700771</v>
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>26.0392984500904</v>
+        <v>26.0420412021165</v>
       </c>
       <c r="E66">
         <v>90</v>
@@ -3746,22 +3746,22 @@
         <v>3</v>
       </c>
       <c r="H66">
+        <v>90</v>
+      </c>
+      <c r="I66">
+        <v>7</v>
+      </c>
+      <c r="J66">
+        <v>3</v>
+      </c>
+      <c r="K66">
         <v>98.05005047</v>
       </c>
-      <c r="I66">
+      <c r="L66">
         <v>0.195456105</v>
       </c>
-      <c r="J66">
+      <c r="M66">
         <v>1.754493424</v>
-      </c>
-      <c r="K66">
-        <v>90</v>
-      </c>
-      <c r="L66">
-        <v>7</v>
-      </c>
-      <c r="M66">
-        <v>3</v>
       </c>
       <c r="AC66">
         <v>0.003090983885</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>35.6225724784244</v>
+        <v>35.6287711216105</v>
       </c>
       <c r="E67">
         <v>89</v>
@@ -3796,22 +3796,22 @@
         <v>4</v>
       </c>
       <c r="H67">
+        <v>89</v>
+      </c>
+      <c r="I67">
+        <v>7</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+      <c r="K67">
         <v>97.59190733</v>
       </c>
-      <c r="I67">
+      <c r="L67">
         <v>0.1437455171</v>
       </c>
-      <c r="J67">
+      <c r="M67">
         <v>2.264347156</v>
-      </c>
-      <c r="K67">
-        <v>89</v>
-      </c>
-      <c r="L67">
-        <v>7</v>
-      </c>
-      <c r="M67">
-        <v>4</v>
       </c>
       <c r="AC67">
         <v>0.002411375725</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>48.1930092862369</v>
+        <v>48.2037973533879</v>
       </c>
       <c r="E68">
         <v>88</v>
@@ -3846,22 +3846,22 @@
         <v>5</v>
       </c>
       <c r="H68">
+        <v>88</v>
+      </c>
+      <c r="I68">
+        <v>7</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68">
         <v>97.09339009</v>
       </c>
-      <c r="I68">
+      <c r="L68">
         <v>0.1085067549</v>
       </c>
-      <c r="J68">
+      <c r="M68">
         <v>2.798103158</v>
-      </c>
-      <c r="K68">
-        <v>88</v>
-      </c>
-      <c r="L68">
-        <v>7</v>
-      </c>
-      <c r="M68">
-        <v>5</v>
       </c>
       <c r="AC68">
         <v>0.00188637531</v>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>19.8841650484914</v>
+        <v>19.8844562615646</v>
       </c>
       <c r="E69">
         <v>92</v>
@@ -3896,19 +3896,19 @@
         <v>0</v>
       </c>
       <c r="H69">
+        <v>92</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
         <v>99.18641971</v>
       </c>
-      <c r="I69">
+      <c r="L69">
         <v>0.8135802875</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>92</v>
-      </c>
-      <c r="L69">
-        <v>8</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>20.251853913356</v>
+        <v>20.2525331266828</v>
       </c>
       <c r="E70">
         <v>91</v>
@@ -3943,31 +3943,31 @@
         <v>1</v>
       </c>
       <c r="H70">
+        <v>91</v>
+      </c>
+      <c r="I70">
+        <v>8</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
         <v>98.84134693</v>
       </c>
-      <c r="I70">
+      <c r="L70">
         <v>0.4884513325</v>
       </c>
-      <c r="J70">
+      <c r="M70">
         <v>0.6702017327999999</v>
       </c>
-      <c r="K70">
-        <v>91</v>
-      </c>
-      <c r="L70">
-        <v>8</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
       <c r="AC70">
-        <v>0.003871704405</v>
+        <v>0.003871704407</v>
       </c>
       <c r="AD70">
-        <v>-0.003708865011</v>
+        <v>-0.003708865012</v>
       </c>
       <c r="AE70">
-        <v>-0.0001628393948</v>
+        <v>-0.0001628393949</v>
       </c>
     </row>
     <row r="71" spans="1:31">
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>12.3998648739168</v>
+        <v>12.3983065834765</v>
       </c>
       <c r="E71">
         <v>96</v>
@@ -3993,22 +3993,22 @@
         <v>4</v>
       </c>
       <c r="H71">
+        <v>96</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+      <c r="K71">
         <v>97.54146434</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
         <v>2.458535663</v>
-      </c>
-      <c r="K71">
-        <v>96</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>4</v>
       </c>
       <c r="AC71">
         <v>0.001243121699</v>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>23.0449128368327</v>
+        <v>23.0470667782294</v>
       </c>
       <c r="E72">
         <v>90</v>
@@ -4040,22 +4040,22 @@
         <v>2</v>
       </c>
       <c r="H72">
+        <v>90</v>
+      </c>
+      <c r="I72">
+        <v>8</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="K72">
         <v>98.46087455</v>
       </c>
-      <c r="I72">
+      <c r="L72">
         <v>0.3235982638</v>
       </c>
-      <c r="J72">
+      <c r="M72">
         <v>1.215527185</v>
-      </c>
-      <c r="K72">
-        <v>90</v>
-      </c>
-      <c r="L72">
-        <v>8</v>
-      </c>
-      <c r="M72">
-        <v>2</v>
       </c>
       <c r="AC72">
         <v>0.003670938202</v>
@@ -4078,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>29.7179146366311</v>
+        <v>29.7231049220126</v>
       </c>
       <c r="E73">
         <v>89</v>
@@ -4090,22 +4090,22 @@
         <v>3</v>
       </c>
       <c r="H73">
+        <v>89</v>
+      </c>
+      <c r="I73">
+        <v>8</v>
+      </c>
+      <c r="J73">
+        <v>3</v>
+      </c>
+      <c r="K73">
         <v>98.04581109</v>
       </c>
-      <c r="I73">
+      <c r="L73">
         <v>0.2288748827</v>
       </c>
-      <c r="J73">
+      <c r="M73">
         <v>1.725314029</v>
-      </c>
-      <c r="K73">
-        <v>89</v>
-      </c>
-      <c r="L73">
-        <v>8</v>
-      </c>
-      <c r="M73">
-        <v>3</v>
       </c>
       <c r="AC73">
         <v>0.003043158618</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>40.1973416945686</v>
+        <v>40.2069479619917</v>
       </c>
       <c r="E74">
         <v>88</v>
@@ -4140,22 +4140,22 @@
         <v>4</v>
       </c>
       <c r="H74">
+        <v>88</v>
+      </c>
+      <c r="I74">
+        <v>8</v>
+      </c>
+      <c r="J74">
+        <v>4</v>
+      </c>
+      <c r="K74">
         <v>97.58868029999999</v>
       </c>
-      <c r="I74">
+      <c r="L74">
         <v>0.1687479064</v>
       </c>
-      <c r="J74">
+      <c r="M74">
         <v>2.242571796</v>
-      </c>
-      <c r="K74">
-        <v>88</v>
-      </c>
-      <c r="L74">
-        <v>8</v>
-      </c>
-      <c r="M74">
-        <v>4</v>
       </c>
       <c r="AC74">
         <v>0.002384698363</v>
@@ -4164,7 +4164,7 @@
         <v>-0.001947664449</v>
       </c>
       <c r="AE74">
-        <v>-0.000437033914</v>
+        <v>-0.0004370339141</v>
       </c>
     </row>
     <row r="75" spans="1:31">
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>53.7358859666696</v>
+        <v>53.7512219639261</v>
       </c>
       <c r="E75">
         <v>87</v>
@@ -4190,22 +4190,22 @@
         <v>5</v>
       </c>
       <c r="H75">
+        <v>87</v>
+      </c>
+      <c r="I75">
+        <v>8</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
+      <c r="K75">
         <v>97.08493987999999</v>
       </c>
-      <c r="I75">
+      <c r="L75">
         <v>0.1274679898</v>
       </c>
-      <c r="J75">
+      <c r="M75">
         <v>2.787592129</v>
-      </c>
-      <c r="K75">
-        <v>87</v>
-      </c>
-      <c r="L75">
-        <v>8</v>
-      </c>
-      <c r="M75">
-        <v>5</v>
       </c>
       <c r="AC75">
         <v>0.001876151969</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>22.6068592544332</v>
+        <v>22.6087992136951</v>
       </c>
       <c r="E76">
         <v>91</v>
@@ -4240,19 +4240,19 @@
         <v>0</v>
       </c>
       <c r="H76">
+        <v>91</v>
+      </c>
+      <c r="I76">
+        <v>9</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
         <v>99.07686151999999</v>
       </c>
-      <c r="I76">
+      <c r="L76">
         <v>0.9231384751</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>91</v>
-      </c>
-      <c r="L76">
-        <v>9</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>23.0059531862502</v>
+        <v>23.0084349220077</v>
       </c>
       <c r="E77">
         <v>90</v>
@@ -4287,22 +4287,22 @@
         <v>1</v>
       </c>
       <c r="H77">
+        <v>90</v>
+      </c>
+      <c r="I77">
+        <v>9</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
         <v>98.79479634</v>
       </c>
-      <c r="I77">
+      <c r="L77">
         <v>0.5576503313</v>
       </c>
-      <c r="J77">
+      <c r="M77">
         <v>0.6475533253</v>
-      </c>
-      <c r="K77">
-        <v>90</v>
-      </c>
-      <c r="L77">
-        <v>9</v>
-      </c>
-      <c r="M77">
-        <v>1</v>
       </c>
       <c r="AC77">
         <v>0.003822329579</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>26.2321548168754</v>
+        <v>26.236560869221</v>
       </c>
       <c r="E78">
         <v>89</v>
@@ -4337,22 +4337,22 @@
         <v>2</v>
       </c>
       <c r="H78">
+        <v>89</v>
+      </c>
+      <c r="I78">
+        <v>9</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78">
         <v>98.44257483</v>
       </c>
-      <c r="I78">
+      <c r="L78">
         <v>0.3715739328</v>
       </c>
-      <c r="J78">
+      <c r="M78">
         <v>1.185851233</v>
-      </c>
-      <c r="K78">
-        <v>89</v>
-      </c>
-      <c r="L78">
-        <v>9</v>
-      </c>
-      <c r="M78">
-        <v>2</v>
       </c>
       <c r="AC78">
         <v>0.003598809163</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>33.696792716061</v>
+        <v>33.7051134013386</v>
       </c>
       <c r="E79">
         <v>88</v>
@@ -4387,22 +4387,22 @@
         <v>3</v>
       </c>
       <c r="H79">
+        <v>88</v>
+      </c>
+      <c r="I79">
+        <v>9</v>
+      </c>
+      <c r="J79">
+        <v>3</v>
+      </c>
+      <c r="K79">
         <v>98.03858106</v>
       </c>
-      <c r="I79">
+      <c r="L79">
         <v>0.2639186241</v>
       </c>
-      <c r="J79">
+      <c r="M79">
         <v>1.697500314</v>
-      </c>
-      <c r="K79">
-        <v>88</v>
-      </c>
-      <c r="L79">
-        <v>9</v>
-      </c>
-      <c r="M79">
-        <v>3</v>
       </c>
       <c r="AC79">
         <v>0.002978149826</v>
@@ -4425,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>45.1691621067827</v>
+        <v>45.18311634414</v>
       </c>
       <c r="E80">
         <v>87</v>
@@ -4437,22 +4437,22 @@
         <v>4</v>
       </c>
       <c r="H80">
+        <v>87</v>
+      </c>
+      <c r="I80">
+        <v>9</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+      <c r="K80">
         <v>97.58265093999999</v>
       </c>
-      <c r="I80">
+      <c r="L80">
         <v>0.1950540385</v>
       </c>
-      <c r="J80">
+      <c r="M80">
         <v>2.222295019</v>
-      </c>
-      <c r="K80">
-        <v>87</v>
-      </c>
-      <c r="L80">
-        <v>9</v>
-      </c>
-      <c r="M80">
-        <v>4</v>
       </c>
       <c r="AC80">
         <v>0.00234203533</v>
@@ -4461,7 +4461,7 @@
         <v>-0.001948644175</v>
       </c>
       <c r="AE80">
-        <v>-0.0003933911551</v>
+        <v>-0.0003933911552</v>
       </c>
     </row>
     <row r="81" spans="1:31">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>59.7490303387053</v>
+        <v>59.7701091118895</v>
       </c>
       <c r="E81">
         <v>86</v>
@@ -4487,22 +4487,22 @@
         <v>5</v>
       </c>
       <c r="H81">
+        <v>86</v>
+      </c>
+      <c r="I81">
+        <v>9</v>
+      </c>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81">
         <v>97.07375491000001</v>
       </c>
-      <c r="I81">
+      <c r="L81">
         <v>0.1474139152</v>
       </c>
-      <c r="J81">
+      <c r="M81">
         <v>2.778831176</v>
-      </c>
-      <c r="K81">
-        <v>86</v>
-      </c>
-      <c r="L81">
-        <v>9</v>
-      </c>
-      <c r="M81">
-        <v>5</v>
       </c>
       <c r="AC81">
         <v>0.001852650848</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>20.3309581322109</v>
+        <v>20.3299474486927</v>
       </c>
       <c r="E82">
         <v>95</v>
@@ -4537,22 +4537,22 @@
         <v>5</v>
       </c>
       <c r="H82">
+        <v>95</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>5</v>
+      </c>
+      <c r="K82">
         <v>97.08192855</v>
       </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
         <v>2.91807145</v>
-      </c>
-      <c r="K82">
-        <v>95</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>5</v>
       </c>
       <c r="AC82">
         <v>0.001023974841</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>25.4067912422686</v>
+        <v>25.410665667064</v>
       </c>
       <c r="E83">
         <v>90</v>
@@ -4584,19 +4584,19 @@
         <v>0</v>
       </c>
       <c r="H83">
+        <v>90</v>
+      </c>
+      <c r="I83">
+        <v>10</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
         <v>98.96493483</v>
       </c>
-      <c r="I83">
+      <c r="L83">
         <v>1.035065168</v>
-      </c>
-      <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="K83">
-        <v>90</v>
-      </c>
-      <c r="L83">
-        <v>10</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -4619,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>25.8773781083443</v>
+        <v>25.8820149981587</v>
       </c>
       <c r="E84">
         <v>89</v>
@@ -4631,22 +4631,22 @@
         <v>1</v>
       </c>
       <c r="H84">
+        <v>89</v>
+      </c>
+      <c r="I84">
+        <v>10</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
         <v>98.74502851</v>
       </c>
-      <c r="I84">
+      <c r="L84">
         <v>0.6291154802</v>
       </c>
-      <c r="J84">
+      <c r="M84">
         <v>0.6258560053</v>
-      </c>
-      <c r="K84">
-        <v>89</v>
-      </c>
-      <c r="L84">
-        <v>10</v>
-      </c>
-      <c r="M84">
-        <v>1</v>
       </c>
       <c r="AC84">
         <v>0.003765069965</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>29.6364315880948</v>
+        <v>29.6437292136424</v>
       </c>
       <c r="E85">
         <v>88</v>
@@ -4681,22 +4681,22 @@
         <v>2</v>
       </c>
       <c r="H85">
+        <v>88</v>
+      </c>
+      <c r="I85">
+        <v>10</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
         <v>98.42099512999999</v>
       </c>
-      <c r="I85">
+      <c r="L85">
         <v>0.4215913859</v>
       </c>
-      <c r="J85">
+      <c r="M85">
         <v>1.157413481</v>
-      </c>
-      <c r="K85">
-        <v>88</v>
-      </c>
-      <c r="L85">
-        <v>10</v>
-      </c>
-      <c r="M85">
-        <v>2</v>
       </c>
       <c r="AC85">
         <v>0.003515210388</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>38.0046386669281</v>
+        <v>38.0171052829405</v>
       </c>
       <c r="E86">
         <v>87</v>
@@ -4731,31 +4731,31 @@
         <v>3</v>
       </c>
       <c r="H86">
+        <v>87</v>
+      </c>
+      <c r="I86">
+        <v>10</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+      <c r="K86">
         <v>98.02827597</v>
       </c>
-      <c r="I86">
+      <c r="L86">
         <v>0.3006877488</v>
       </c>
-      <c r="J86">
+      <c r="M86">
         <v>1.671036286</v>
       </c>
-      <c r="K86">
-        <v>87</v>
-      </c>
-      <c r="L86">
-        <v>10</v>
-      </c>
-      <c r="M86">
-        <v>3</v>
-      </c>
       <c r="AC86">
-        <v>0.002900682483</v>
+        <v>0.002900682482</v>
       </c>
       <c r="AD86">
-        <v>-0.002551160136</v>
+        <v>-0.002551160135</v>
       </c>
       <c r="AE86">
-        <v>-0.0003495223472</v>
+        <v>-0.0003495223471</v>
       </c>
     </row>
     <row r="87" spans="1:31">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>50.5668854365623</v>
+        <v>50.5863126397785</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -4781,22 +4781,22 @@
         <v>4</v>
       </c>
       <c r="H87">
+        <v>86</v>
+      </c>
+      <c r="I87">
+        <v>10</v>
+      </c>
+      <c r="J87">
+        <v>4</v>
+      </c>
+      <c r="K87">
         <v>97.57373839</v>
       </c>
-      <c r="I87">
+      <c r="L87">
         <v>0.2227356936</v>
       </c>
-      <c r="J87">
+      <c r="M87">
         <v>2.203525921</v>
-      </c>
-      <c r="K87">
-        <v>86</v>
-      </c>
-      <c r="L87">
-        <v>10</v>
-      </c>
-      <c r="M87">
-        <v>4</v>
       </c>
       <c r="AC87">
         <v>0.002287785994</v>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>66.26795604992451</v>
+        <v>66.2885429436141</v>
       </c>
       <c r="E88">
         <v>85</v>
@@ -4831,22 +4831,22 @@
         <v>5</v>
       </c>
       <c r="H88">
+        <v>85</v>
+      </c>
+      <c r="I88">
+        <v>10</v>
+      </c>
+      <c r="J88">
+        <v>5</v>
+      </c>
+      <c r="K88">
         <v>97.05974955000001</v>
       </c>
-      <c r="I88">
+      <c r="L88">
         <v>0.1683865499</v>
       </c>
-      <c r="J88">
+      <c r="M88">
         <v>2.771863899</v>
-      </c>
-      <c r="K88">
-        <v>85</v>
-      </c>
-      <c r="L88">
-        <v>10</v>
-      </c>
-      <c r="M88">
-        <v>5</v>
       </c>
       <c r="AC88">
         <v>0.001819208308</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>28.2929501077219</v>
+        <v>28.2990674491026</v>
       </c>
       <c r="E89">
         <v>89</v>
@@ -4881,19 +4881,19 @@
         <v>0</v>
       </c>
       <c r="H89">
+        <v>89</v>
+      </c>
+      <c r="I89">
+        <v>11</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
         <v>98.85039666999999</v>
       </c>
-      <c r="I89">
+      <c r="L89">
         <v>1.149603328</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>89</v>
-      </c>
-      <c r="L89">
-        <v>11</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>28.8863721431918</v>
+        <v>28.8935646732993</v>
       </c>
       <c r="E90">
         <v>88</v>
@@ -4928,22 +4928,22 @@
         <v>1</v>
       </c>
       <c r="H90">
+        <v>88</v>
+      </c>
+      <c r="I90">
+        <v>11</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
         <v>98.69189821000001</v>
       </c>
-      <c r="I90">
+      <c r="L90">
         <v>0.7030237566</v>
       </c>
-      <c r="J90">
+      <c r="M90">
         <v>0.6050780368000001</v>
-      </c>
-      <c r="K90">
-        <v>88</v>
-      </c>
-      <c r="L90">
-        <v>11</v>
-      </c>
-      <c r="M90">
-        <v>1</v>
       </c>
       <c r="AC90">
         <v>0.003700328615</v>
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>33.2845229268316</v>
+        <v>33.2951372209222</v>
       </c>
       <c r="E91">
         <v>87</v>
@@ -4978,22 +4978,22 @@
         <v>2</v>
       </c>
       <c r="H91">
+        <v>87</v>
+      </c>
+      <c r="I91">
+        <v>11</v>
+      </c>
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="K91">
         <v>98.39602601999999</v>
       </c>
-      <c r="I91">
+      <c r="L91">
         <v>0.4737904468</v>
       </c>
-      <c r="J91">
+      <c r="M91">
         <v>1.130183532</v>
-      </c>
-      <c r="K91">
-        <v>87</v>
-      </c>
-      <c r="L91">
-        <v>11</v>
-      </c>
-      <c r="M91">
-        <v>2</v>
       </c>
       <c r="AC91">
         <v>0.003422509162</v>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>42.6708273893686</v>
+        <v>42.6879642645025</v>
       </c>
       <c r="E92">
         <v>86</v>
@@ -5028,22 +5028,22 @@
         <v>3</v>
       </c>
       <c r="H92">
+        <v>86</v>
+      </c>
+      <c r="I92">
+        <v>11</v>
+      </c>
+      <c r="J92">
+        <v>3</v>
+      </c>
+      <c r="K92">
         <v>98.01480183</v>
       </c>
-      <c r="I92">
+      <c r="L92">
         <v>0.3392907559</v>
       </c>
-      <c r="J92">
+      <c r="M92">
         <v>1.645907412</v>
-      </c>
-      <c r="K92">
-        <v>86</v>
-      </c>
-      <c r="L92">
-        <v>11</v>
-      </c>
-      <c r="M92">
-        <v>3</v>
       </c>
       <c r="AC92">
         <v>0.002814361181</v>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2.34858587676698</v>
+        <v>2.35628812173576</v>
       </c>
       <c r="E93">
         <v>99</v>
@@ -5078,19 +5078,19 @@
         <v>0</v>
       </c>
       <c r="H93">
+        <v>99</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
         <v>99.90302268000001</v>
       </c>
-      <c r="I93">
+      <c r="L93">
         <v>0.09697731773</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>99</v>
-      </c>
-      <c r="L93">
-        <v>1</v>
       </c>
       <c r="M93">
         <v>0</v>
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>56.4201849731564</v>
+        <v>56.4465194426664</v>
       </c>
       <c r="E94">
         <v>85</v>
@@ -5125,22 +5125,22 @@
         <v>4</v>
       </c>
       <c r="H94">
+        <v>85</v>
+      </c>
+      <c r="I94">
+        <v>11</v>
+      </c>
+      <c r="J94">
+        <v>4</v>
+      </c>
+      <c r="K94">
         <v>97.56185415</v>
       </c>
-      <c r="I94">
+      <c r="L94">
         <v>0.2518688747</v>
       </c>
-      <c r="J94">
+      <c r="M94">
         <v>2.186276977</v>
-      </c>
-      <c r="K94">
-        <v>85</v>
-      </c>
-      <c r="L94">
-        <v>11</v>
-      </c>
-      <c r="M94">
-        <v>4</v>
       </c>
       <c r="AC94">
         <v>0.002225319703</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>73.30650832577059</v>
+        <v>73.3352074950562</v>
       </c>
       <c r="E95">
         <v>84</v>
@@ -5175,22 +5175,22 @@
         <v>5</v>
       </c>
       <c r="H95">
+        <v>84</v>
+      </c>
+      <c r="I95">
+        <v>11</v>
+      </c>
+      <c r="J95">
+        <v>5</v>
+      </c>
+      <c r="K95">
         <v>97.04283168000001</v>
       </c>
-      <c r="I95">
+      <c r="L95">
         <v>0.1904282498</v>
       </c>
-      <c r="J95">
+      <c r="M95">
         <v>2.766740073</v>
-      </c>
-      <c r="K95">
-        <v>84</v>
-      </c>
-      <c r="L95">
-        <v>11</v>
-      </c>
-      <c r="M95">
-        <v>5</v>
       </c>
       <c r="AC95">
         <v>0.001778452791</v>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>31.274975703663</v>
+        <v>31.2836708783208</v>
       </c>
       <c r="E96">
         <v>88</v>
@@ -5225,19 +5225,19 @@
         <v>0</v>
       </c>
       <c r="H96">
+        <v>88</v>
+      </c>
+      <c r="I96">
+        <v>12</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
         <v>98.73297731</v>
       </c>
-      <c r="I96">
+      <c r="L96">
         <v>1.267022686</v>
-      </c>
-      <c r="J96">
-        <v>0</v>
-      </c>
-      <c r="K96">
-        <v>88</v>
-      </c>
-      <c r="L96">
-        <v>12</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>32.0538864794655</v>
+        <v>32.0640933975003</v>
       </c>
       <c r="E97">
         <v>87</v>
@@ -5272,22 +5272,22 @@
         <v>1</v>
       </c>
       <c r="H97">
+        <v>87</v>
+      </c>
+      <c r="I97">
+        <v>12</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
         <v>98.63524141000001</v>
       </c>
-      <c r="I97">
+      <c r="L97">
         <v>0.7795704832</v>
       </c>
-      <c r="J97">
+      <c r="M97">
         <v>0.5851881115999999</v>
-      </c>
-      <c r="K97">
-        <v>87</v>
-      </c>
-      <c r="L97">
-        <v>12</v>
-      </c>
-      <c r="M97">
-        <v>1</v>
       </c>
       <c r="AC97">
         <v>0.003628621432</v>
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>37.2038820128977</v>
+        <v>37.2185655102154</v>
       </c>
       <c r="E98">
         <v>86</v>
@@ -5322,25 +5322,25 @@
         <v>2</v>
       </c>
       <c r="H98">
+        <v>86</v>
+      </c>
+      <c r="I98">
+        <v>12</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="K98">
         <v>98.36754424999999</v>
       </c>
-      <c r="I98">
+      <c r="L98">
         <v>0.528324161</v>
       </c>
-      <c r="J98">
+      <c r="M98">
         <v>1.104131593</v>
       </c>
-      <c r="K98">
-        <v>86</v>
-      </c>
-      <c r="L98">
-        <v>12</v>
-      </c>
-      <c r="M98">
-        <v>2</v>
-      </c>
       <c r="AC98">
-        <v>0.003322719148</v>
+        <v>0.003322719147</v>
       </c>
       <c r="AD98">
         <v>-0.003082039812</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>47.7254211845939</v>
+        <v>47.7483875962101</v>
       </c>
       <c r="E99">
         <v>85</v>
@@ -5372,22 +5372,22 @@
         <v>3</v>
       </c>
       <c r="H99">
+        <v>85</v>
+      </c>
+      <c r="I99">
+        <v>12</v>
+      </c>
+      <c r="J99">
+        <v>3</v>
+      </c>
+      <c r="K99">
         <v>97.99805424</v>
       </c>
-      <c r="I99">
+      <c r="L99">
         <v>0.379844976</v>
       </c>
-      <c r="J99">
+      <c r="M99">
         <v>1.622100781</v>
-      </c>
-      <c r="K99">
-        <v>85</v>
-      </c>
-      <c r="L99">
-        <v>12</v>
-      </c>
-      <c r="M99">
-        <v>3</v>
       </c>
       <c r="AC99">
         <v>0.002721988894</v>
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>62.7593985319559</v>
+        <v>62.7937713168134</v>
       </c>
       <c r="E100">
         <v>84</v>
@@ -5422,22 +5422,22 @@
         <v>4</v>
       </c>
       <c r="H100">
+        <v>84</v>
+      </c>
+      <c r="I100">
+        <v>12</v>
+      </c>
+      <c r="J100">
+        <v>4</v>
+      </c>
+      <c r="K100">
         <v>97.5469016</v>
       </c>
-      <c r="I100">
+      <c r="L100">
         <v>0.2825340017</v>
       </c>
-      <c r="J100">
+      <c r="M100">
         <v>2.170564402</v>
-      </c>
-      <c r="K100">
-        <v>84</v>
-      </c>
-      <c r="L100">
-        <v>12</v>
-      </c>
-      <c r="M100">
-        <v>4</v>
       </c>
       <c r="AC100">
         <v>0.002157232856</v>
@@ -5460,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>80.9004897814623</v>
+        <v>80.938683233757</v>
       </c>
       <c r="E101">
         <v>83</v>
@@ -5472,22 +5472,22 @@
         <v>5</v>
       </c>
       <c r="H101">
+        <v>83</v>
+      </c>
+      <c r="I101">
+        <v>12</v>
+      </c>
+      <c r="J101">
+        <v>5</v>
+      </c>
+      <c r="K101">
         <v>97.02290237</v>
       </c>
-      <c r="I101">
+      <c r="L101">
         <v>0.2135813232</v>
       </c>
-      <c r="J101">
+      <c r="M101">
         <v>2.763516302</v>
-      </c>
-      <c r="K101">
-        <v>83</v>
-      </c>
-      <c r="L101">
-        <v>12</v>
-      </c>
-      <c r="M101">
-        <v>5</v>
       </c>
       <c r="AC101">
         <v>0.001732456579</v>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>34.3631732617335</v>
+        <v>34.3748118852233</v>
       </c>
       <c r="E102">
         <v>87</v>
@@ -5522,19 +5522,19 @@
         <v>0</v>
       </c>
       <c r="H102">
+        <v>87</v>
+      </c>
+      <c r="I102">
+        <v>13</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
         <v>98.61237668</v>
       </c>
-      <c r="I102">
+      <c r="L102">
         <v>1.387623322</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102">
-        <v>87</v>
-      </c>
-      <c r="L102">
-        <v>13</v>
       </c>
       <c r="M102">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>35.4016224002295</v>
+        <v>35.4153713821918</v>
       </c>
       <c r="E103">
         <v>86</v>
@@ -5569,28 +5569,28 @@
         <v>1</v>
       </c>
       <c r="H103">
+        <v>86</v>
+      </c>
+      <c r="I103">
+        <v>13</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103">
         <v>98.5748731</v>
       </c>
-      <c r="I103">
+      <c r="L103">
         <v>0.8589714878</v>
       </c>
-      <c r="J103">
+      <c r="M103">
         <v>0.566155408</v>
       </c>
-      <c r="K103">
-        <v>86</v>
-      </c>
-      <c r="L103">
-        <v>13</v>
-      </c>
-      <c r="M103">
-        <v>1</v>
-      </c>
       <c r="AC103">
-        <v>0.00355055092</v>
+        <v>0.003550550918</v>
       </c>
       <c r="AD103">
-        <v>-0.0034280516</v>
+        <v>-0.003428051599</v>
       </c>
       <c r="AE103">
         <v>-0.0001224993192</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>2.70528436275608</v>
+        <v>2.70949507342104</v>
       </c>
       <c r="E104">
         <v>98</v>
@@ -5619,22 +5619,22 @@
         <v>1</v>
       </c>
       <c r="H104">
+        <v>98</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
         <v>99.08617044</v>
       </c>
-      <c r="I104">
+      <c r="L104">
         <v>0.05574880139</v>
       </c>
-      <c r="J104">
+      <c r="M104">
         <v>0.8580807544</v>
-      </c>
-      <c r="K104">
-        <v>98</v>
-      </c>
-      <c r="L104">
-        <v>1</v>
-      </c>
-      <c r="M104">
-        <v>1</v>
       </c>
       <c r="AC104">
         <v>0.00400825365</v>
@@ -5657,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>41.422662497955</v>
+        <v>41.4422979386418</v>
       </c>
       <c r="E105">
         <v>85</v>
@@ -5669,22 +5669,22 @@
         <v>2</v>
       </c>
       <c r="H105">
+        <v>85</v>
+      </c>
+      <c r="I105">
+        <v>13</v>
+      </c>
+      <c r="J105">
+        <v>2</v>
+      </c>
+      <c r="K105">
         <v>98.33541115</v>
       </c>
-      <c r="I105">
+      <c r="L105">
         <v>0.5853602645</v>
       </c>
-      <c r="J105">
+      <c r="M105">
         <v>1.079228586</v>
-      </c>
-      <c r="K105">
-        <v>85</v>
-      </c>
-      <c r="L105">
-        <v>13</v>
-      </c>
-      <c r="M105">
-        <v>2</v>
       </c>
       <c r="AC105">
         <v>0.0032175906</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>53.1992064187112</v>
+        <v>53.229852142554</v>
       </c>
       <c r="E106">
         <v>84</v>
@@ -5719,31 +5719,31 @@
         <v>3</v>
       </c>
       <c r="H106">
+        <v>84</v>
+      </c>
+      <c r="I106">
+        <v>13</v>
+      </c>
+      <c r="J106">
+        <v>3</v>
+      </c>
+      <c r="K106">
         <v>97.97791718000001</v>
       </c>
-      <c r="I106">
+      <c r="L106">
         <v>0.4224774558</v>
       </c>
-      <c r="J106">
+      <c r="M106">
         <v>1.599605368</v>
       </c>
-      <c r="K106">
-        <v>84</v>
-      </c>
-      <c r="L106">
-        <v>13</v>
-      </c>
-      <c r="M106">
-        <v>3</v>
-      </c>
       <c r="AC106">
-        <v>0.002625771515</v>
+        <v>0.002625771514</v>
       </c>
       <c r="AD106">
-        <v>-0.002362719174</v>
+        <v>-0.002362719173</v>
       </c>
       <c r="AE106">
-        <v>-0.000263052341</v>
+        <v>-0.0002630523409</v>
       </c>
     </row>
     <row r="107" spans="1:31">
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>69.6231278173691</v>
+        <v>69.66046712865349</v>
       </c>
       <c r="E107">
         <v>83</v>
@@ -5769,22 +5769,22 @@
         <v>4</v>
       </c>
       <c r="H107">
+        <v>83</v>
+      </c>
+      <c r="I107">
+        <v>13</v>
+      </c>
+      <c r="J107">
+        <v>4</v>
+      </c>
+      <c r="K107">
         <v>97.52877535</v>
       </c>
-      <c r="I107">
+      <c r="L107">
         <v>0.3148160986</v>
       </c>
-      <c r="J107">
+      <c r="M107">
         <v>2.156408551</v>
-      </c>
-      <c r="K107">
-        <v>83</v>
-      </c>
-      <c r="L107">
-        <v>13</v>
-      </c>
-      <c r="M107">
-        <v>4</v>
       </c>
       <c r="AC107">
         <v>0.002085540866</v>
@@ -5793,7 +5793,7 @@
         <v>-0.001820917058</v>
       </c>
       <c r="AE107">
-        <v>-0.0002646238078</v>
+        <v>-0.0002646238079</v>
       </c>
     </row>
     <row r="108" spans="1:31">
@@ -5807,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>89.079226838179</v>
+        <v>89.13009897630771</v>
       </c>
       <c r="E108">
         <v>82</v>
@@ -5819,22 +5819,22 @@
         <v>5</v>
       </c>
       <c r="H108">
+        <v>82</v>
+      </c>
+      <c r="I108">
+        <v>13</v>
+      </c>
+      <c r="J108">
+        <v>5</v>
+      </c>
+      <c r="K108">
         <v>96.9998557</v>
       </c>
-      <c r="I108">
+      <c r="L108">
         <v>0.2378875392</v>
       </c>
-      <c r="J108">
+      <c r="M108">
         <v>2.76225676</v>
-      </c>
-      <c r="K108">
-        <v>82</v>
-      </c>
-      <c r="L108">
-        <v>13</v>
-      </c>
-      <c r="M108">
-        <v>5</v>
       </c>
       <c r="AC108">
         <v>0.001682852607</v>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>37.5686748654618</v>
+        <v>37.5836581529024</v>
       </c>
       <c r="E109">
         <v>86</v>
@@ -5869,19 +5869,19 @@
         <v>0</v>
       </c>
       <c r="H109">
+        <v>86</v>
+      </c>
+      <c r="I109">
+        <v>14</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
         <v>98.48826012000001</v>
       </c>
-      <c r="I109">
+      <c r="L109">
         <v>1.511739881</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>86</v>
-      </c>
-      <c r="L109">
-        <v>14</v>
       </c>
       <c r="M109">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>38.9520378389744</v>
+        <v>38.9699384880154</v>
       </c>
       <c r="E110">
         <v>85</v>
@@ -5916,22 +5916,22 @@
         <v>1</v>
       </c>
       <c r="H110">
+        <v>85</v>
+      </c>
+      <c r="I110">
+        <v>14</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
         <v>98.51058473000001</v>
       </c>
-      <c r="I110">
+      <c r="L110">
         <v>0.9414656135</v>
       </c>
-      <c r="J110">
+      <c r="M110">
         <v>0.5479496564</v>
-      </c>
-      <c r="K110">
-        <v>85</v>
-      </c>
-      <c r="L110">
-        <v>14</v>
-      </c>
-      <c r="M110">
-        <v>1</v>
       </c>
       <c r="AC110">
         <v>0.003466787271</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>45.9697394438199</v>
+        <v>45.9956603368342</v>
       </c>
       <c r="E111">
         <v>84</v>
@@ -5966,22 +5966,22 @@
         <v>2</v>
       </c>
       <c r="H111">
+        <v>84</v>
+      </c>
+      <c r="I111">
+        <v>14</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111">
         <v>98.29947084</v>
       </c>
-      <c r="I111">
+      <c r="L111">
         <v>0.6450828872</v>
       </c>
-      <c r="J111">
+      <c r="M111">
         <v>1.055446274</v>
-      </c>
-      <c r="K111">
-        <v>84</v>
-      </c>
-      <c r="L111">
-        <v>14</v>
-      </c>
-      <c r="M111">
-        <v>2</v>
       </c>
       <c r="AC111">
         <v>0.003108658626</v>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>59.1237181054429</v>
+        <v>59.1633911558165</v>
       </c>
       <c r="E112">
         <v>83</v>
@@ -6016,22 +6016,22 @@
         <v>3</v>
       </c>
       <c r="H112">
+        <v>83</v>
+      </c>
+      <c r="I112">
+        <v>14</v>
+      </c>
+      <c r="J112">
+        <v>3</v>
+      </c>
+      <c r="K112">
         <v>97.95426191999999</v>
       </c>
-      <c r="I112">
+      <c r="L112">
         <v>0.467325907</v>
       </c>
-      <c r="J112">
+      <c r="M112">
         <v>1.578412176</v>
-      </c>
-      <c r="K112">
-        <v>83</v>
-      </c>
-      <c r="L112">
-        <v>14</v>
-      </c>
-      <c r="M112">
-        <v>3</v>
       </c>
       <c r="AC112">
         <v>0.002527446492</v>
@@ -6054,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>77.0286895120642</v>
+        <v>77.0777153090097</v>
       </c>
       <c r="E113">
         <v>82</v>
@@ -6066,22 +6066,22 @@
         <v>4</v>
       </c>
       <c r="H113">
+        <v>82</v>
+      </c>
+      <c r="I113">
+        <v>14</v>
+      </c>
+      <c r="J113">
+        <v>4</v>
+      </c>
+      <c r="K113">
         <v>97.50736067</v>
       </c>
-      <c r="I113">
+      <c r="L113">
         <v>0.3488049671</v>
       </c>
-      <c r="J113">
+      <c r="M113">
         <v>2.143834363</v>
-      </c>
-      <c r="K113">
-        <v>82</v>
-      </c>
-      <c r="L113">
-        <v>14</v>
-      </c>
-      <c r="M113">
-        <v>4</v>
       </c>
       <c r="AC113">
         <v>0.002011804777</v>
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>97.872445371213</v>
+        <v>97.9381689592507</v>
       </c>
       <c r="E114">
         <v>81</v>
@@ -6116,22 +6116,22 @@
         <v>5</v>
       </c>
       <c r="H114">
+        <v>81</v>
+      </c>
+      <c r="I114">
+        <v>14</v>
+      </c>
+      <c r="J114">
+        <v>5</v>
+      </c>
+      <c r="K114">
         <v>96.97357848</v>
       </c>
-      <c r="I114">
+      <c r="L114">
         <v>0.2633875032</v>
       </c>
-      <c r="J114">
+      <c r="M114">
         <v>2.763034016</v>
-      </c>
-      <c r="K114">
-        <v>81</v>
-      </c>
-      <c r="L114">
-        <v>14</v>
-      </c>
-      <c r="M114">
-        <v>5</v>
       </c>
       <c r="AC114">
         <v>0.001630925405</v>
@@ -6154,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>4.69178971650866</v>
+        <v>4.68897263815832</v>
       </c>
       <c r="E115">
         <v>97</v>
@@ -6166,22 +6166,22 @@
         <v>2</v>
       </c>
       <c r="H115">
+        <v>97</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115">
         <v>98.50401189</v>
       </c>
-      <c r="I115">
+      <c r="L115">
         <v>0.03544621377</v>
       </c>
-      <c r="J115">
+      <c r="M115">
         <v>1.460541892</v>
-      </c>
-      <c r="K115">
-        <v>97</v>
-      </c>
-      <c r="L115">
-        <v>1</v>
-      </c>
-      <c r="M115">
-        <v>2</v>
       </c>
       <c r="AC115">
         <v>0.003207686439</v>
@@ -6204,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>40.9026700517052</v>
+        <v>40.9214391708158</v>
       </c>
       <c r="E116">
         <v>85</v>
@@ -6216,19 +6216,19 @@
         <v>0</v>
       </c>
       <c r="H116">
+        <v>85</v>
+      </c>
+      <c r="I116">
+        <v>15</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
         <v>98.36025339</v>
       </c>
-      <c r="I116">
+      <c r="L116">
         <v>1.639746609</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>85</v>
-      </c>
-      <c r="L116">
-        <v>15</v>
       </c>
       <c r="M116">
         <v>0</v>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>42.7283462314463</v>
+        <v>42.751103827757</v>
       </c>
       <c r="E117">
         <v>84</v>
@@ -6263,22 +6263,22 @@
         <v>1</v>
       </c>
       <c r="H117">
+        <v>84</v>
+      </c>
+      <c r="I117">
+        <v>15</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
         <v>98.44214114</v>
       </c>
-      <c r="I117">
+      <c r="L117">
         <v>1.027317673</v>
       </c>
-      <c r="J117">
+      <c r="M117">
         <v>0.5305411864</v>
-      </c>
-      <c r="K117">
-        <v>84</v>
-      </c>
-      <c r="L117">
-        <v>15</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
       </c>
       <c r="AC117">
         <v>0.003378049268</v>
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>50.8747358418765</v>
+        <v>50.9079550067904</v>
       </c>
       <c r="E118">
         <v>83</v>
@@ -6313,22 +6313,22 @@
         <v>2</v>
       </c>
       <c r="H118">
+        <v>83</v>
+      </c>
+      <c r="I118">
+        <v>15</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118">
         <v>98.2595481</v>
       </c>
-      <c r="I118">
+      <c r="L118">
         <v>0.7076945296</v>
       </c>
-      <c r="J118">
+      <c r="M118">
         <v>1.032757371</v>
-      </c>
-      <c r="K118">
-        <v>83</v>
-      </c>
-      <c r="L118">
-        <v>15</v>
-      </c>
-      <c r="M118">
-        <v>2</v>
       </c>
       <c r="AC118">
         <v>0.002997269524</v>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>65.53122669888241</v>
+        <v>65.5818244097529</v>
       </c>
       <c r="E119">
         <v>82</v>
@@ -6363,22 +6363,22 @@
         <v>3</v>
       </c>
       <c r="H119">
+        <v>82</v>
+      </c>
+      <c r="I119">
+        <v>15</v>
+      </c>
+      <c r="J119">
+        <v>3</v>
+      </c>
+      <c r="K119">
         <v>97.92694569</v>
       </c>
-      <c r="I119">
+      <c r="L119">
         <v>0.5145398231</v>
       </c>
-      <c r="J119">
+      <c r="M119">
         <v>1.55851449</v>
-      </c>
-      <c r="K119">
-        <v>82</v>
-      </c>
-      <c r="L119">
-        <v>15</v>
-      </c>
-      <c r="M119">
-        <v>3</v>
       </c>
       <c r="AC119">
         <v>0.002428398217</v>
@@ -6401,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>85.01530552649319</v>
+        <v>85.0785347525058</v>
       </c>
       <c r="E120">
         <v>81</v>
@@ -6413,22 +6413,22 @@
         <v>4</v>
       </c>
       <c r="H120">
+        <v>81</v>
+      </c>
+      <c r="I120">
+        <v>15</v>
+      </c>
+      <c r="J120">
+        <v>4</v>
+      </c>
+      <c r="K120">
         <v>97.48253281</v>
       </c>
-      <c r="I120">
+      <c r="L120">
         <v>0.3845953365</v>
       </c>
-      <c r="J120">
+      <c r="M120">
         <v>2.132871854</v>
-      </c>
-      <c r="K120">
-        <v>81</v>
-      </c>
-      <c r="L120">
-        <v>15</v>
-      </c>
-      <c r="M120">
-        <v>4</v>
       </c>
       <c r="AC120">
         <v>0.001937231567</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>107.310232982575</v>
+        <v>107.39384746139</v>
       </c>
       <c r="E121">
         <v>80</v>
@@ -6463,22 +6463,22 @@
         <v>5</v>
       </c>
       <c r="H121">
+        <v>80</v>
+      </c>
+      <c r="I121">
+        <v>15</v>
+      </c>
+      <c r="J121">
+        <v>5</v>
+      </c>
+      <c r="K121">
         <v>96.94395016</v>
       </c>
-      <c r="I121">
+      <c r="L121">
         <v>0.2901198704</v>
       </c>
-      <c r="J121">
+      <c r="M121">
         <v>2.76592997</v>
-      </c>
-      <c r="K121">
-        <v>80</v>
-      </c>
-      <c r="L121">
-        <v>15</v>
-      </c>
-      <c r="M121">
-        <v>5</v>
       </c>
       <c r="AC121">
         <v>0.00157768276</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>44.3779333186759</v>
+        <v>44.4009767492673</v>
       </c>
       <c r="E122">
         <v>84</v>
@@ -6513,19 +6513,19 @@
         <v>0</v>
       </c>
       <c r="H122">
+        <v>84</v>
+      </c>
+      <c r="I122">
+        <v>16</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
         <v>98.22793669000001</v>
       </c>
-      <c r="I122">
+      <c r="L122">
         <v>1.772063307</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>84</v>
-      </c>
-      <c r="L122">
-        <v>16</v>
       </c>
       <c r="M122">
         <v>0</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>46.7545230869543</v>
+        <v>46.7829543844034</v>
       </c>
       <c r="E123">
         <v>83</v>
@@ -6560,28 +6560,28 @@
         <v>1</v>
       </c>
       <c r="H123">
+        <v>83</v>
+      </c>
+      <c r="I123">
+        <v>16</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
         <v>98.36927710000001</v>
       </c>
-      <c r="I123">
+      <c r="L123">
         <v>1.116821939</v>
       </c>
-      <c r="J123">
+      <c r="M123">
         <v>0.5139009638000001</v>
       </c>
-      <c r="K123">
-        <v>83</v>
-      </c>
-      <c r="L123">
-        <v>16</v>
-      </c>
-      <c r="M123">
-        <v>1</v>
-      </c>
       <c r="AC123">
-        <v>0.003285085265</v>
+        <v>0.003285085266</v>
       </c>
       <c r="AD123">
-        <v>-0.00318118298</v>
+        <v>-0.003181182981</v>
       </c>
       <c r="AE123">
         <v>-0.000103902285</v>
@@ -6598,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>56.1680385653139</v>
+        <v>56.209985256263</v>
       </c>
       <c r="E124">
         <v>82</v>
@@ -6610,22 +6610,22 @@
         <v>2</v>
       </c>
       <c r="H124">
+        <v>82</v>
+      </c>
+      <c r="I124">
+        <v>16</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="K124">
         <v>98.21544600999999</v>
       </c>
-      <c r="I124">
+      <c r="L124">
         <v>0.7734183578</v>
       </c>
-      <c r="J124">
+      <c r="M124">
         <v>1.011135633</v>
-      </c>
-      <c r="K124">
-        <v>82</v>
-      </c>
-      <c r="L124">
-        <v>16</v>
-      </c>
-      <c r="M124">
-        <v>2</v>
       </c>
       <c r="AC124">
         <v>0.002884608044</v>
@@ -6648,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>72.462404686482</v>
+        <v>72.51867276311511</v>
       </c>
       <c r="E125">
         <v>81</v>
@@ -6660,25 +6660,25 @@
         <v>3</v>
       </c>
       <c r="H125">
+        <v>81</v>
+      </c>
+      <c r="I125">
+        <v>16</v>
+      </c>
+      <c r="J125">
+        <v>3</v>
+      </c>
+      <c r="K125">
         <v>97.89581019000001</v>
       </c>
-      <c r="I125">
+      <c r="L125">
         <v>0.5642817272</v>
       </c>
-      <c r="J125">
+      <c r="M125">
         <v>1.53990808</v>
       </c>
-      <c r="K125">
-        <v>81</v>
-      </c>
-      <c r="L125">
-        <v>16</v>
-      </c>
-      <c r="M125">
-        <v>3</v>
-      </c>
       <c r="AC125">
-        <v>0.002329704698</v>
+        <v>0.002329704697</v>
       </c>
       <c r="AD125">
         <v>-0.002128386017</v>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>8.74102832628771</v>
+        <v>8.73889417100904</v>
       </c>
       <c r="E126">
         <v>96</v>
@@ -6710,22 +6710,22 @@
         <v>3</v>
       </c>
       <c r="H126">
+        <v>96</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>3</v>
+      </c>
+      <c r="K126">
         <v>98.01641563</v>
       </c>
-      <c r="I126">
+      <c r="L126">
         <v>0.02430416582</v>
       </c>
-      <c r="J126">
+      <c r="M126">
         <v>1.959280203</v>
-      </c>
-      <c r="K126">
-        <v>96</v>
-      </c>
-      <c r="L126">
-        <v>1</v>
-      </c>
-      <c r="M126">
-        <v>3</v>
       </c>
       <c r="AC126">
         <v>0.002307382697</v>
@@ -6739,7 +6739,7 @@
     </row>
     <row r="127" spans="1:31">
       <c r="A127">
-        <v>933.4727259</v>
+        <v>933.473</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -6748,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>0.0199999999999818</v>
+        <v>0.0202740999999378</v>
       </c>
       <c r="E127">
         <v>100</v>
